--- a/Chase_positions_9-4-2026_copy..xlsx
+++ b/Chase_positions_9-4-2026_copy..xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alanl\GitHub\Stock_Picker\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Alan/GitHub/Stock_Picker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E1543D7-0D79-4FCD-9BD8-457A61EBDC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8560BC8-FAE2-3241-891C-942F925339D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="0" windowWidth="21600" windowHeight="12960" xr2:uid="{3324304A-3E17-4BFC-9364-F5FD2F7F66E8}"/>
+    <workbookView xWindow="30340" yWindow="2420" windowWidth="21600" windowHeight="15080" xr2:uid="{3324304A-3E17-4BFC-9364-F5FD2F7F66E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Chase_positions_9-4-2026" sheetId="1" r:id="rId1"/>
@@ -512,9 +512,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="170" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="173" formatCode="0.0"/>
-    <numFmt numFmtId="174" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -1225,7 +1225,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1236,43 +1236,43 @@
     <xf numFmtId="0" fontId="16" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1287,25 +1287,25 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1314,37 +1314,37 @@
     <xf numFmtId="0" fontId="18" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="16" fillId="33" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="33" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="34" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1353,49 +1353,49 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="16" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="16" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1413,28 +1413,25 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="16" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="35" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1443,22 +1440,22 @@
     <xf numFmtId="3" fontId="16" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1855,82 +1852,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C60FFEC6-5E0C-473D-88D0-539DE50A3FD4}">
   <dimension ref="A1:BT35"/>
-  <sheetFormatPr defaultRowHeight="13.8" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.75" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="2" max="2" width="12.625" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="10.25" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="31.375" style="4" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="8.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.796875" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="2" max="2" width="12.59765625" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="10.19921875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="31.3984375" style="4" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="8.3984375" style="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" style="19" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="11.25" style="15" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="7.25" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="11.19921875" style="15" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="7.19921875" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="9" max="9" width="6" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="7.375" style="4" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="6.125" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="8.25" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="7.875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="7.3984375" style="4" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.59765625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="6.19921875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="8.19921875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="7.796875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="15" max="15" width="14" style="15" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="8.625" style="34" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.5" style="4" customWidth="1"/>
-    <col min="19" max="19" width="6.125" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="10.25" style="4" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="8.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.125" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="23" width="10.25" style="4" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="6.875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="25" max="25" width="7.125" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="26" max="26" width="6.25" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="27" max="27" width="10.5" style="4" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="10.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.25" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="30" width="10.5" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="31" max="31" width="10.875" style="15" customWidth="1" collapsed="1"/>
+    <col min="16" max="16" width="8.59765625" style="34" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.19921875" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.3984375" style="4" customWidth="1"/>
+    <col min="19" max="19" width="6.19921875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="10.19921875" style="4" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" width="8.796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.19921875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="10.19921875" style="4" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="6.796875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="7.19921875" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="26" max="26" width="6.19921875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="27" max="27" width="10.3984375" style="4" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="28" max="28" width="10.19921875" style="4" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.19921875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="30" width="10.3984375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="31" max="31" width="10.796875" style="15" customWidth="1" collapsed="1"/>
     <col min="32" max="32" width="10" style="15" customWidth="1" collapsed="1"/>
-    <col min="33" max="33" width="10.125" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="34" max="34" width="10.5" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="33" width="10.19921875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="34" max="34" width="10.3984375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="35" max="35" width="10" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="36" max="36" width="11" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="37" max="37" width="10.875" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="38" max="38" width="8.25" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="39" max="39" width="9.625" style="4" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="40" max="40" width="9.625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="41" max="41" width="8.625" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="42" max="42" width="8.625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="43" max="43" width="9.75" style="4" customWidth="1" collapsed="1"/>
-    <col min="44" max="44" width="9.125" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="45" max="45" width="5.875" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="46" max="46" width="8.625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="47" max="47" width="8.5" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="48" max="48" width="6.5" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="49" max="49" width="7.375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="37" max="37" width="10.796875" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="38" max="38" width="8.19921875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="39" max="39" width="9.59765625" style="4" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="40" max="40" width="9.59765625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="41" max="41" width="8.59765625" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="42" max="42" width="8.59765625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="43" max="43" width="9.796875" style="4" customWidth="1" collapsed="1"/>
+    <col min="44" max="44" width="9.19921875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="45" max="45" width="5.796875" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="46" max="46" width="8.59765625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="47" max="47" width="8.3984375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="48" max="48" width="6.3984375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="49" max="49" width="7.3984375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="50" max="50" width="10" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="51" max="51" width="10.25" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="51" max="51" width="10.19921875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="52" max="53" width="9" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="54" max="54" width="7.875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="54" max="54" width="7.796875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="55" max="55" width="10" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="56" max="56" width="8.625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="57" max="57" width="12.375" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="58" max="58" width="12.375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="59" max="59" width="11.625" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="60" max="61" width="8.625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="62" max="62" width="9.125" style="15" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="63" max="63" width="7.125" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="64" max="64" width="11.5" style="15" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="65" max="65" width="8.375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="66" max="66" width="10.875" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="67" max="67" width="12.375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="56" max="56" width="8.59765625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="57" max="57" width="12.3984375" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="58" max="58" width="12.3984375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="59" max="59" width="11.59765625" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="60" max="61" width="8.59765625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="62" max="62" width="9.19921875" style="15" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="63" max="63" width="7.19921875" style="15" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="64" max="64" width="11.3984375" style="15" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="65" max="65" width="8.3984375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="66" max="66" width="10.796875" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="67" max="67" width="12.3984375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="68" max="68" width="9" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="69" max="69" width="8.25" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="70" max="70" width="8.375" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="69" max="69" width="8.19921875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="70" max="70" width="8.3984375" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="71" max="71" width="14" style="15" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="72" max="72" width="9" style="4" collapsed="1"/>
     <col min="73" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:72" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2144,15 +2141,15 @@
       <c r="BS1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="BT1" s="65" t="s">
+      <c r="BT1" s="64" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A2" s="77"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="76" t="s">
+    <row r="2" spans="1:72" x14ac:dyDescent="0.15">
+      <c r="A2" s="76"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="75" t="s">
         <v>152</v>
       </c>
       <c r="E2" s="28"/>
@@ -2223,7 +2220,7 @@
       <c r="BR2" s="27"/>
       <c r="BS2" s="30"/>
     </row>
-    <row r="3" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:72" ht="24" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>77</v>
       </c>
@@ -2353,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="7"/>
-      <c r="BJ3" s="69">
+      <c r="BJ3" s="68">
         <v>46272</v>
       </c>
       <c r="BK3" s="6" t="s">
@@ -2373,12 +2370,12 @@
       <c r="BS3" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="BT3" s="66">
+      <c r="BT3" s="65">
         <f>P3/P$26</f>
         <v>0.16835456163037987</v>
       </c>
     </row>
-    <row r="4" spans="1:72" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:72" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="6" t="s">
         <v>77</v>
       </c>
@@ -2504,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="7"/>
-      <c r="BJ4" s="69">
+      <c r="BJ4" s="68">
         <v>46272</v>
       </c>
       <c r="BK4" s="6" t="s">
@@ -2524,12 +2521,12 @@
       <c r="BS4" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="BT4" s="66">
+      <c r="BT4" s="65">
         <f t="shared" ref="BT4:BT12" si="0">P4/P$26</f>
         <v>9.0543796972330282E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:72" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:72" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>77</v>
       </c>
@@ -2659,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="7"/>
-      <c r="BJ5" s="69">
+      <c r="BJ5" s="68">
         <v>46272</v>
       </c>
       <c r="BK5" s="6" t="s">
@@ -2679,12 +2676,12 @@
       <c r="BS5" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="BT5" s="66">
+      <c r="BT5" s="65">
         <f t="shared" si="0"/>
         <v>5.7129766941407249E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:72" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:72" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="6" t="s">
         <v>77</v>
       </c>
@@ -2814,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="BI6" s="7"/>
-      <c r="BJ6" s="69">
+      <c r="BJ6" s="68">
         <v>46272</v>
       </c>
       <c r="BK6" s="6" t="s">
@@ -2834,12 +2831,12 @@
       <c r="BS6" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="BT6" s="66">
+      <c r="BT6" s="65">
         <f t="shared" si="0"/>
         <v>4.5083820988022952E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:72" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:72" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="6" t="s">
         <v>77</v>
       </c>
@@ -2969,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="7"/>
-      <c r="BJ7" s="69">
+      <c r="BJ7" s="68">
         <v>46272</v>
       </c>
       <c r="BK7" s="6" t="s">
@@ -2989,12 +2986,12 @@
       <c r="BS7" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="BT7" s="66">
+      <c r="BT7" s="65">
         <f t="shared" si="0"/>
         <v>4.1625973741237783E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:72" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:72" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="6" t="s">
         <v>77</v>
       </c>
@@ -3124,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="BI8" s="7"/>
-      <c r="BJ8" s="69">
+      <c r="BJ8" s="68">
         <v>46272</v>
       </c>
       <c r="BK8" s="6" t="s">
@@ -3144,12 +3141,12 @@
       <c r="BS8" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="BT8" s="66">
+      <c r="BT8" s="65">
         <f t="shared" si="0"/>
         <v>3.6667153992530149E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:72" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:72" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="6" t="s">
         <v>77</v>
       </c>
@@ -3275,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="7"/>
-      <c r="BJ9" s="69">
+      <c r="BJ9" s="68">
         <v>46272</v>
       </c>
       <c r="BK9" s="6" t="s">
@@ -3295,12 +3292,12 @@
       <c r="BS9" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="BT9" s="66">
+      <c r="BT9" s="65">
         <f t="shared" si="0"/>
         <v>3.2127695336735811E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:72" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:72" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="6" t="s">
         <v>77</v>
       </c>
@@ -3426,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="7"/>
-      <c r="BJ10" s="69">
+      <c r="BJ10" s="68">
         <v>46272</v>
       </c>
       <c r="BK10" s="6" t="s">
@@ -3446,12 +3443,12 @@
       <c r="BS10" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="BT10" s="66">
+      <c r="BT10" s="65">
         <f t="shared" si="0"/>
         <v>3.1797763900467339E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:72" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:72" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="38" t="s">
         <v>77</v>
       </c>
@@ -3577,7 +3574,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="39"/>
-      <c r="BJ11" s="70">
+      <c r="BJ11" s="69">
         <v>46272</v>
       </c>
       <c r="BK11" s="38" t="s">
@@ -3597,12 +3594,12 @@
       <c r="BS11" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="BT11" s="66">
+      <c r="BT11" s="65">
         <f t="shared" si="0"/>
         <v>1.1561195434107037E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:72" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:72" ht="13.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A12" s="38"/>
       <c r="B12" s="38"/>
       <c r="C12" s="39"/>
@@ -3664,7 +3661,7 @@
       <c r="BG12" s="47"/>
       <c r="BH12" s="39"/>
       <c r="BI12" s="39"/>
-      <c r="BJ12" s="70"/>
+      <c r="BJ12" s="69"/>
       <c r="BK12" s="38"/>
       <c r="BL12" s="38"/>
       <c r="BM12" s="39"/>
@@ -3674,12 +3671,12 @@
       <c r="BQ12" s="39"/>
       <c r="BR12" s="39"/>
       <c r="BS12" s="38"/>
-      <c r="BT12" s="67">
+      <c r="BT12" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:72" x14ac:dyDescent="0.15">
       <c r="A13" s="48"/>
       <c r="B13" s="49"/>
       <c r="C13" s="50"/>
@@ -3717,11 +3714,11 @@
       <c r="X13" s="50"/>
       <c r="Y13" s="50"/>
       <c r="Z13" s="50"/>
-      <c r="AA13" s="72">
+      <c r="AA13" s="71">
         <f>SUM(AA3:AA12)</f>
         <v>19050.679999999997</v>
       </c>
-      <c r="AB13" s="72">
+      <c r="AB13" s="71">
         <f>SUM(AB3:AB12)</f>
         <v>19050.679999999997</v>
       </c>
@@ -3738,14 +3735,14 @@
       <c r="AJ13" s="50"/>
       <c r="AK13" s="50"/>
       <c r="AL13" s="50"/>
-      <c r="AM13" s="72">
+      <c r="AM13" s="71">
         <f>SUM(AM3:AM12)</f>
         <v>872.4</v>
       </c>
       <c r="AN13" s="50"/>
       <c r="AO13" s="50"/>
       <c r="AP13" s="50"/>
-      <c r="AQ13" s="72">
+      <c r="AQ13" s="71">
         <f>SUM(AQ3:AQ12)</f>
         <v>1424.1399999999999</v>
       </c>
@@ -3777,28 +3774,28 @@
       <c r="BQ13" s="50"/>
       <c r="BR13" s="50"/>
       <c r="BS13" s="54"/>
-      <c r="BT13" s="64">
+      <c r="BT13" s="63">
         <f>SUM(BT3:BT12)</f>
         <v>0.51489172893721846</v>
       </c>
     </row>
-    <row r="14" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:72" x14ac:dyDescent="0.15">
       <c r="A14" s="11"/>
       <c r="BS14" s="24"/>
     </row>
-    <row r="15" spans="1:72" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:72" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="11"/>
       <c r="BJ15" s="4"/>
       <c r="BK15" s="4"/>
       <c r="BL15" s="4"/>
       <c r="BS15" s="4"/>
-      <c r="BT15" s="78"/>
+      <c r="BT15" s="77"/>
     </row>
-    <row r="16" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A16" s="77"/>
-      <c r="B16" s="75"/>
-      <c r="C16" s="75"/>
-      <c r="D16" s="76" t="s">
+    <row r="16" spans="1:72" x14ac:dyDescent="0.15">
+      <c r="A16" s="76"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="75" t="s">
         <v>153</v>
       </c>
       <c r="E16" s="28"/>
@@ -3869,7 +3866,7 @@
       <c r="BR16" s="27"/>
       <c r="BS16" s="30"/>
     </row>
-    <row r="17" spans="1:72" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:72" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="6" t="s">
         <v>77</v>
       </c>
@@ -3999,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="7"/>
-      <c r="BJ17" s="69">
+      <c r="BJ17" s="68">
         <v>46272</v>
       </c>
       <c r="BK17" s="6" t="s">
@@ -4019,12 +4016,12 @@
       <c r="BS17" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="BT17" s="66">
+      <c r="BT17" s="65">
         <f t="shared" ref="BT17:BT23" si="1">P17/P$26</f>
         <v>3.8196013161578425E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:72" s="63" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:72" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="58" t="s">
         <v>68</v>
       </c>
@@ -4154,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="59"/>
-      <c r="BJ18" s="71">
+      <c r="BJ18" s="70">
         <v>46272</v>
       </c>
       <c r="BK18" s="58" t="s">
@@ -4174,12 +4171,12 @@
       <c r="BS18" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="BT18" s="66">
+      <c r="BT18" s="65">
         <f t="shared" si="1"/>
         <v>0.16881500664786972</v>
       </c>
     </row>
-    <row r="19" spans="1:72" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:72" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="6" t="s">
         <v>68</v>
       </c>
@@ -4309,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="7"/>
-      <c r="BJ19" s="69">
+      <c r="BJ19" s="68">
         <v>46272</v>
       </c>
       <c r="BK19" s="6" t="s">
@@ -4331,12 +4328,12 @@
       <c r="BS19" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="BT19" s="66">
+      <c r="BT19" s="65">
         <f t="shared" si="1"/>
         <v>0.1155920589780793</v>
       </c>
     </row>
-    <row r="20" spans="1:72" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:72" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="6" t="s">
         <v>68</v>
       </c>
@@ -4468,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="7"/>
-      <c r="BJ20" s="69">
+      <c r="BJ20" s="68">
         <v>46272</v>
       </c>
       <c r="BK20" s="6" t="s">
@@ -4490,12 +4487,12 @@
       <c r="BS20" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="BT20" s="66">
+      <c r="BT20" s="65">
         <f t="shared" si="1"/>
         <v>3.4152380110459714E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:72" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:72" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="6" t="s">
         <v>83</v>
       </c>
@@ -4517,7 +4514,7 @@
         <v>73</v>
       </c>
       <c r="I21" s="7"/>
-      <c r="J21" s="74">
+      <c r="J21" s="73">
         <v>1</v>
       </c>
       <c r="K21" s="7" t="b">
@@ -4619,7 +4616,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="7"/>
-      <c r="BJ21" s="69">
+      <c r="BJ21" s="68">
         <v>46272</v>
       </c>
       <c r="BK21" s="6" t="s">
@@ -4637,12 +4634,12 @@
       <c r="BQ21" s="7"/>
       <c r="BR21" s="7"/>
       <c r="BS21" s="6"/>
-      <c r="BT21" s="66">
+      <c r="BT21" s="65">
         <f t="shared" si="1"/>
         <v>6.1473024159171387E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:72" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:72" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="6" t="s">
         <v>83</v>
       </c>
@@ -4666,7 +4663,7 @@
         <v>73</v>
       </c>
       <c r="I22" s="7"/>
-      <c r="J22" s="74">
+      <c r="J22" s="73">
         <v>1</v>
       </c>
       <c r="K22" s="7" t="b">
@@ -4772,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="7"/>
-      <c r="BJ22" s="69">
+      <c r="BJ22" s="68">
         <v>46272</v>
       </c>
       <c r="BK22" s="6" t="s">
@@ -4794,12 +4791,12 @@
       <c r="BS22" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="BT22" s="66">
+      <c r="BT22" s="65">
         <f t="shared" si="1"/>
         <v>0.12220550974887706</v>
       </c>
     </row>
-    <row r="23" spans="1:72" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:72" ht="13.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
@@ -4861,7 +4858,7 @@
       <c r="BG23" s="9"/>
       <c r="BH23" s="7"/>
       <c r="BI23" s="7"/>
-      <c r="BJ23" s="69"/>
+      <c r="BJ23" s="68"/>
       <c r="BK23" s="6"/>
       <c r="BL23" s="6"/>
       <c r="BM23" s="7"/>
@@ -4871,12 +4868,12 @@
       <c r="BQ23" s="7"/>
       <c r="BR23" s="7"/>
       <c r="BS23" s="6"/>
-      <c r="BT23" s="67">
+      <c r="BT23" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:72" x14ac:dyDescent="0.15">
       <c r="A24" s="48"/>
       <c r="B24" s="49"/>
       <c r="C24" s="50"/>
@@ -4914,11 +4911,11 @@
       <c r="X24" s="50"/>
       <c r="Y24" s="50"/>
       <c r="Z24" s="50"/>
-      <c r="AA24" s="72">
+      <c r="AA24" s="71">
         <f>SUM(AA17:AA23)</f>
         <v>14098.810000000001</v>
       </c>
-      <c r="AB24" s="72">
+      <c r="AB24" s="71">
         <f>SUM(AB17:AB23)</f>
         <v>14131.480000000001</v>
       </c>
@@ -4935,14 +4932,14 @@
       <c r="AJ24" s="50"/>
       <c r="AK24" s="50"/>
       <c r="AL24" s="50"/>
-      <c r="AM24" s="72">
+      <c r="AM24" s="71">
         <f>SUM(AM17:AM23)</f>
         <v>31059.41</v>
       </c>
-      <c r="AN24" s="73"/>
-      <c r="AO24" s="73"/>
-      <c r="AP24" s="73"/>
-      <c r="AQ24" s="72">
+      <c r="AN24" s="72"/>
+      <c r="AO24" s="72"/>
+      <c r="AP24" s="72"/>
+      <c r="AQ24" s="71">
         <f>SUM(AQ17:AQ23)</f>
         <v>8232.02</v>
       </c>
@@ -4974,19 +4971,19 @@
       <c r="BQ24" s="50"/>
       <c r="BR24" s="50"/>
       <c r="BS24" s="54"/>
-      <c r="BT24" s="64">
+      <c r="BT24" s="63">
         <f>SUM(BT17:BT23)</f>
         <v>0.48510827106278137</v>
       </c>
     </row>
-    <row r="25" spans="1:72" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:72" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A25" s="11"/>
       <c r="BS25" s="24"/>
     </row>
-    <row r="26" spans="1:72" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:72" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="11"/>
       <c r="D26" s="56"/>
-      <c r="E26" s="68" t="s">
+      <c r="E26" s="67" t="s">
         <v>155</v>
       </c>
       <c r="P26" s="56">
@@ -5024,25 +5021,25 @@
       </c>
       <c r="BS26" s="24"/>
     </row>
-    <row r="27" spans="1:72" ht="14.4" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:72" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A27" s="11"/>
       <c r="BS27" s="24"/>
     </row>
-    <row r="28" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:72" x14ac:dyDescent="0.15">
       <c r="A28" s="11"/>
       <c r="BS28" s="24"/>
     </row>
-    <row r="29" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:72" x14ac:dyDescent="0.15">
       <c r="A29" s="11"/>
       <c r="BS29" s="24"/>
     </row>
-    <row r="30" spans="1:72" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:72" ht="14" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>140</v>
       </c>
       <c r="BS30" s="24"/>
     </row>
-    <row r="31" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:72" x14ac:dyDescent="0.15">
       <c r="A31" s="23" t="s">
         <v>141</v>
       </c>
@@ -5051,7 +5048,7 @@
       </c>
       <c r="BS31" s="24"/>
     </row>
-    <row r="32" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:72" x14ac:dyDescent="0.15">
       <c r="A32" s="23" t="s">
         <v>124</v>
       </c>
@@ -5060,7 +5057,7 @@
       </c>
       <c r="BS32" s="24"/>
     </row>
-    <row r="33" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:71" x14ac:dyDescent="0.15">
       <c r="A33" s="23" t="s">
         <v>144</v>
       </c>
@@ -5069,7 +5066,7 @@
       </c>
       <c r="BS33" s="24"/>
     </row>
-    <row r="34" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:71" x14ac:dyDescent="0.15">
       <c r="A34" s="23" t="s">
         <v>93</v>
       </c>
@@ -5078,7 +5075,7 @@
       </c>
       <c r="BS34" s="24"/>
     </row>
-    <row r="35" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:71" x14ac:dyDescent="0.15">
       <c r="A35" s="23" t="s">
         <v>147</v>
       </c>
@@ -5156,18 +5153,18 @@
       <c r="BS35" s="25"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AA27:AA1048576 AE27:AE1048576 AA1:AA17 AE1:AE17 AE19:AE25 AA19:AA25">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
+  <conditionalFormatting sqref="AA1:AA25 AE1:AE25">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF27:AF1048576 AF1:AF17 AF19:AF25">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="AA27:AA1048576">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA18 AE18">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="AF1:AF17 AF19:AF25 AE27:AF1048576">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
